--- a/Stats Sheet/Round Gaps/Realm Navigation.xlsx
+++ b/Stats Sheet/Round Gaps/Realm Navigation.xlsx
@@ -31,6 +31,9 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
     <x:t>aalaan</x:t>
   </x:si>
   <x:si>
@@ -43,6 +46,9 @@
     <x:t>BoltsInCharge</x:t>
   </x:si>
   <x:si>
+    <x:t>154</x:t>
+  </x:si>
+  <x:si>
     <x:t>Brodator</x:t>
   </x:si>
   <x:si>
@@ -109,6 +115,9 @@
     <x:t>powermc</x:t>
   </x:si>
   <x:si>
+    <x:t>394</x:t>
+  </x:si>
+  <x:si>
     <x:t>Randehh</x:t>
   </x:si>
   <x:si>
@@ -118,6 +127,9 @@
     <x:t>TheSlimeBrother</x:t>
   </x:si>
   <x:si>
+    <x:t>360</x:t>
+  </x:si>
+  <x:si>
     <x:t>ToucanTom</x:t>
   </x:si>
   <x:si>
@@ -206,6 +218,18 @@
   </x:si>
   <x:si>
     <x:t>TehBaconBrawlerZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_Fost_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bobbytheturtle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ryfri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SharkeyJaws</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -564,10 +588,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:J59"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:9" s="1" customFormat="1">
+    <x:row r="1" spans="1:10" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45718</x:v>
       </x:c>
@@ -583,8 +607,11 @@
       <x:c r="I1" s="1">
         <x:v>46102</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9">
+      <x:c r="J1" s="1">
+        <x:v>46112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10">
       <x:c r="F2" s="0">
         <x:v>34</x:v>
       </x:c>
@@ -597,8 +624,11 @@
       <x:c r="I2" s="0">
         <x:v>144</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
+      <x:c r="J2" s="0">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -614,94 +644,106 @@
       <x:c r="I3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
+      <x:c r="J3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="0">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:10">
+      <x:c r="A6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
-      <x:c r="A6" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="0">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:10">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -710,73 +752,79 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:10">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:10">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:9">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -785,21 +833,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:9">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -808,21 +856,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:10">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -831,47 +879,50 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
@@ -880,44 +931,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -926,24 +980,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
@@ -952,21 +1006,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
@@ -975,41 +1029,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -1018,18 +1075,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:9">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
@@ -1038,24 +1095,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>0</x:v>
@@ -1064,38 +1121,41 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:9">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>0</x:v>
@@ -1104,93 +1164,102 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H25" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:9">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>0</x:v>
@@ -1199,96 +1268,105 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:9">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I31" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:9">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
@@ -1297,15 +1375,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>1</x:v>
@@ -1314,15 +1392,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>1</x:v>
@@ -1331,24 +1409,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>1</x:v>
@@ -1357,18 +1435,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:9">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>1</x:v>
@@ -1377,41 +1455,44 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J37" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>2</x:v>
@@ -1420,15 +1501,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>2</x:v>
@@ -1437,18 +1518,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>2</x:v>
@@ -1457,75 +1538,84 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>3</x:v>
@@ -1534,15 +1624,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>3</x:v>
@@ -1551,15 +1641,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>3</x:v>
@@ -1568,15 +1658,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>3</x:v>
@@ -1585,38 +1675,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>3</x:v>
@@ -1625,35 +1718,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I49" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:10">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I50" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J50" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:10">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>4</x:v>
@@ -1662,32 +1758,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I51" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:10">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I52" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J52" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:10">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>4</x:v>
@@ -1696,32 +1795,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I53" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:10">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I54" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:9">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J54" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:10">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>4</x:v>
@@ -1730,7 +1832,75 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I55" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:10">
+      <x:c r="A56" s="0">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J56" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:10">
+      <x:c r="A57" s="0">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D57" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J57" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:10">
+      <x:c r="A58" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D58" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J58" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:10">
+      <x:c r="A59" s="0">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D59" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J59" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
